--- a/Проект мистер пи тесты.xlsx
+++ b/Проект мистер пи тесты.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kazhi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C0DD3B-E1F2-4BE1-B9F9-96B03D5180FD}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2988A86A-CE30-42F2-A92A-44C3DBDBF030}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
   <si>
     <t>Критерии ЧЯ</t>
   </si>
@@ -88,9 +88,6 @@
     <t>2.2 "введены некоректные данные"</t>
   </si>
   <si>
-    <t>1.7 не число</t>
-  </si>
-  <si>
     <t>1.3 число(триг. Функция)</t>
   </si>
   <si>
@@ -193,9 +190,6 @@
     <t>корень числа равен 2,236i</t>
   </si>
   <si>
-    <t>1.8 число(положительное нет целого корня)</t>
-  </si>
-  <si>
     <t>1.9 число(отрицательное нет целого корня)</t>
   </si>
   <si>
@@ -212,6 +206,21 @@
   </si>
   <si>
     <t>короче все что связано с интерфейсом пока записать сюда</t>
+  </si>
+  <si>
+    <t>1.7 число(логарифм)</t>
+  </si>
+  <si>
+    <t>т10</t>
+  </si>
+  <si>
+    <t>log(2,16)</t>
+  </si>
+  <si>
+    <t>1.10 не число</t>
+  </si>
+  <si>
+    <t>1.8  число(положительное нет целого корня)</t>
   </si>
 </sst>
 </file>
@@ -581,7 +590,7 @@
         <v>0</v>
       </c>
       <c r="M1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -594,49 +603,52 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>15</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>16</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>17</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
         <v>18</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="R3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -644,16 +656,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N4">
         <v>4</v>
       </c>
       <c r="O4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -661,210 +673,228 @@
         <v>4</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N5">
         <v>-4</v>
       </c>
       <c r="O5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N6" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" t="s">
         <v>26</v>
-      </c>
-      <c r="O6" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N8">
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N9" s="5">
         <v>2.25</v>
       </c>
       <c r="O9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="M10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N10" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="O10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M11" t="s">
-        <v>36</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>43</v>
+      <c r="A12" t="s">
+        <v>41</v>
       </c>
       <c r="I12" s="4"/>
       <c r="K12" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N12">
         <v>-5</v>
       </c>
       <c r="O12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="C13" s="4"/>
+      <c r="L13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13" t="s">
+        <v>33</v>
+      </c>
+      <c r="O13" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="C16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Проект мистер пи тесты.xlsx
+++ b/Проект мистер пи тесты.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kazhi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2988A86A-CE30-42F2-A92A-44C3DBDBF030}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0605D62F-949F-4CF4-A398-1B6B7BCDBD60}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -214,13 +214,13 @@
     <t>т10</t>
   </si>
   <si>
-    <t>log(2,16)</t>
-  </si>
-  <si>
     <t>1.10 не число</t>
   </si>
   <si>
     <t>1.8  число(положительное нет целого корня)</t>
+  </si>
+  <si>
+    <t>log_2(16)</t>
   </si>
 </sst>
 </file>
@@ -766,7 +766,7 @@
         <v>32</v>
       </c>
       <c r="N10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O10" t="s">
         <v>37</v>
@@ -774,7 +774,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>22</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C13" s="4"/>
       <c r="L13" s="4" t="s">
